--- a/data/trans_dic/P8_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P8_1_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a hacer esfuerzos moderados</t>
+          <t>Población con limitación a hacer esfuerzos moderados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 16,26</t>
+          <t>8,69; 16,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,47; 21,53</t>
+          <t>12,94; 21,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,75; 24,11</t>
+          <t>14,41; 23,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 19,72</t>
+          <t>11,01; 19,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,16; 23,49</t>
+          <t>13,93; 23,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,13; 34,02</t>
+          <t>23,36; 34,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,73; 33,48</t>
+          <t>22,85; 33,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,96; 22,78</t>
+          <t>15,89; 22,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,22; 18,44</t>
+          <t>12,1; 18,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,27; 26,2</t>
+          <t>19,08; 26,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,93; 27,47</t>
+          <t>19,68; 27,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,58; 19,81</t>
+          <t>14,6; 19,78</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,5; 15,67</t>
+          <t>9,65; 15,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,53; 19,05</t>
+          <t>11,77; 18,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 15,14</t>
+          <t>9,19; 14,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,96; 20,21</t>
+          <t>12,72; 19,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,56; 28,19</t>
+          <t>20,71; 27,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,52; 31,53</t>
+          <t>23,44; 31,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,37; 25,0</t>
+          <t>17,57; 25,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,33; 26,73</t>
+          <t>21,0; 26,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,96; 20,97</t>
+          <t>15,88; 20,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,19; 23,89</t>
+          <t>18,85; 24,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,11; 18,8</t>
+          <t>14,16; 19,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,7; 22,39</t>
+          <t>17,62; 22,41</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,04</t>
+          <t>4,81; 10,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,81; 19,11</t>
+          <t>10,66; 19,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,4; 17,39</t>
+          <t>10,1; 16,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,04; 16,54</t>
+          <t>9,97; 16,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,91; 25,85</t>
+          <t>17,34; 25,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,92; 28,68</t>
+          <t>18,95; 28,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,16; 24,94</t>
+          <t>15,61; 24,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,63; 22,66</t>
+          <t>16,43; 22,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,92; 17,49</t>
+          <t>11,91; 17,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,92; 22,18</t>
+          <t>16,08; 22,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,11; 19,95</t>
+          <t>13,85; 19,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,2; 18,59</t>
+          <t>13,96; 18,59</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 12,45</t>
+          <t>6,72; 12,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,05; 19,51</t>
+          <t>11,22; 18,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,77; 18,0</t>
+          <t>11,01; 18,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,65; 24,34</t>
+          <t>14,42; 24,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,91; 24,91</t>
+          <t>16,78; 25,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,37; 35,82</t>
+          <t>25,96; 35,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,43; 31,16</t>
+          <t>21,78; 31,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,18; 23,17</t>
+          <t>10,99; 23,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,56; 17,64</t>
+          <t>12,15; 17,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,84; 26,04</t>
+          <t>20,05; 26,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,23; 23,52</t>
+          <t>17,21; 23,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,26; 21,9</t>
+          <t>13,5; 21,93</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 11,3</t>
+          <t>4,42; 11,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,55; 22,53</t>
+          <t>11,52; 22,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 17,34</t>
+          <t>8,97; 17,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,71; 16,1</t>
+          <t>8,77; 16,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,11; 22,45</t>
+          <t>12,44; 22,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,46; 34,84</t>
+          <t>22,6; 36,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,75; 28,04</t>
+          <t>17,32; 28,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 25,04</t>
+          <t>10,37; 24,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,04; 15,49</t>
+          <t>9,24; 15,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,77; 26,74</t>
+          <t>18,82; 27,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,25; 21,48</t>
+          <t>13,88; 21,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,03; 19,55</t>
+          <t>11,46; 19,59</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,41; 14,53</t>
+          <t>7,45; 14,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,66; 23,15</t>
+          <t>13,72; 22,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,83; 26,09</t>
+          <t>15,55; 25,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,7; 13,65</t>
+          <t>7,99; 13,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,64; 30,58</t>
+          <t>19,73; 30,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,68; 32,46</t>
+          <t>22,0; 33,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,36; 36,88</t>
+          <t>25,88; 37,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,02; 20,54</t>
+          <t>13,71; 20,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,01; 22,05</t>
+          <t>14,95; 21,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,14; 26,67</t>
+          <t>19,58; 26,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,27; 30,39</t>
+          <t>22,09; 29,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,44; 15,68</t>
+          <t>11,51; 15,88</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,04; 15,03</t>
+          <t>9,78; 15,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,74; 15,04</t>
+          <t>9,67; 15,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,78; 16,56</t>
+          <t>11,04; 16,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,14; 19,44</t>
+          <t>13,45; 19,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,22; 24,48</t>
+          <t>18,33; 24,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,34; 27,01</t>
+          <t>20,2; 26,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,35; 24,81</t>
+          <t>18,54; 24,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,59; 24,67</t>
+          <t>8,03; 24,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,83; 19,09</t>
+          <t>14,8; 18,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,83; 20,06</t>
+          <t>15,97; 20,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,47; 19,94</t>
+          <t>15,5; 19,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,82; 20,66</t>
+          <t>11,17; 20,98</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,8; 15,64</t>
+          <t>10,76; 15,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,81; 17,16</t>
+          <t>11,54; 16,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,56; 14,14</t>
+          <t>9,54; 13,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,56; 71,32</t>
+          <t>12,43; 71,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,15; 24,17</t>
+          <t>18,45; 24,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,4; 24,16</t>
+          <t>18,16; 24,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,84; 22,85</t>
+          <t>16,86; 22,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,95; 27,49</t>
+          <t>21,91; 27,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,3; 19,19</t>
+          <t>15,09; 19,07</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,01; 19,95</t>
+          <t>15,83; 20,02</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,0; 17,74</t>
+          <t>13,83; 17,63</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,47; 57,19</t>
+          <t>18,32; 57,06</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,18; 12,22</t>
+          <t>10,08; 12,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,41; 15,9</t>
+          <t>13,41; 15,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,78; 15,1</t>
+          <t>12,74; 15,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,31; 38,23</t>
+          <t>14,23; 37,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,0; 22,96</t>
+          <t>20,06; 22,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,87; 26,84</t>
+          <t>23,76; 26,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,13; 24,12</t>
+          <t>21,2; 24,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,68; 22,2</t>
+          <t>16,52; 22,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,49; 17,36</t>
+          <t>15,49; 17,21</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,16; 21,2</t>
+          <t>19,15; 21,06</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,45; 19,36</t>
+          <t>17,37; 19,3</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,13; 30,76</t>
+          <t>17,14; 29,77</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a hacer esfuerzos moderados</t>
+          <t>Población con limitación a hacer esfuerzos moderados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23337; 44387</t>
+          <t>23728; 44556</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36753; 63446</t>
+          <t>38127; 64034</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43327; 70825</t>
+          <t>42326; 69762</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35113; 61429</t>
+          <t>34281; 60957</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36946; 61279</t>
+          <t>36347; 62277</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66431; 97730</t>
+          <t>67100; 98364</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65631; 96659</t>
+          <t>65975; 97489</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46238; 65985</t>
+          <t>46025; 66358</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65243; 98463</t>
+          <t>64570; 100169</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>112144; 152467</t>
+          <t>111021; 152514</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116099; 160001</t>
+          <t>114654; 159051</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>87640; 119045</t>
+          <t>87750; 118910</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46823; 77248</t>
+          <t>47595; 76051</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58287; 96316</t>
+          <t>59484; 94032</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47131; 76089</t>
+          <t>46171; 75255</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67208; 104764</t>
+          <t>65915; 102013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>103626; 142086</t>
+          <t>104351; 140449</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>123188; 165145</t>
+          <t>122793; 164681</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90866; 130773</t>
+          <t>91898; 131312</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>104701; 137674</t>
+          <t>108122; 138802</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>159077; 209075</t>
+          <t>158377; 207380</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>187267; 245898</t>
+          <t>194008; 246993</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>144710; 192796</t>
+          <t>145213; 196070</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>182906; 231351</t>
+          <t>182108; 231604</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15722; 35189</t>
+          <t>15336; 34690</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35031; 61920</t>
+          <t>34528; 63450</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33121; 55409</t>
+          <t>32173; 54113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31736; 52270</t>
+          <t>31525; 52247</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>56726; 86708</t>
+          <t>58166; 85364</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64532; 97801</t>
+          <t>64613; 97778</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50999; 83887</t>
+          <t>52485; 83701</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>58045; 79109</t>
+          <t>57363; 79562</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>77988; 114428</t>
+          <t>77895; 113764</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>105890; 147523</t>
+          <t>106961; 148091</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92422; 130669</t>
+          <t>90717; 127635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94481; 123663</t>
+          <t>92848; 123652</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24116; 44640</t>
+          <t>24109; 46354</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41335; 72980</t>
+          <t>41979; 69561</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39833; 66609</t>
+          <t>40718; 68834</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45777; 76091</t>
+          <t>45066; 75955</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>62831; 92516</t>
+          <t>62326; 93921</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>102555; 139313</t>
+          <t>100982; 138691</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82981; 120690</t>
+          <t>84335; 121874</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>48432; 110215</t>
+          <t>52278; 112467</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91723; 128769</t>
+          <t>88704; 127511</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>151390; 198655</t>
+          <t>152948; 199530</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>130462; 178126</t>
+          <t>130337; 177298</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>104489; 172633</t>
+          <t>106379; 172896</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9216; 22971</t>
+          <t>8987; 23024</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24562; 47899</t>
+          <t>24495; 48690</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18222; 36629</t>
+          <t>18939; 37399</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15577; 28771</t>
+          <t>15681; 28849</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25158; 46615</t>
+          <t>25830; 47725</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49331; 76500</t>
+          <t>49638; 79213</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36616; 61301</t>
+          <t>37866; 62299</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>26694; 64657</t>
+          <t>26785; 64279</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37165; 63650</t>
+          <t>37994; 64912</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81124; 115584</t>
+          <t>81347; 117317</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61265; 92340</t>
+          <t>59668; 92006</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>48177; 85423</t>
+          <t>50093; 85609</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20074; 39348</t>
+          <t>20164; 39546</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37432; 63427</t>
+          <t>37596; 62926</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41660; 68659</t>
+          <t>40906; 67457</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20765; 36799</t>
+          <t>21543; 37266</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>54615; 85047</t>
+          <t>54873; 84724</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>60719; 90906</t>
+          <t>61616; 92654</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69268; 100729</t>
+          <t>70670; 101726</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36050; 52804</t>
+          <t>35248; 52365</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>82397; 121055</t>
+          <t>82080; 115548</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>106016; 147737</t>
+          <t>108487; 144985</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>119403; 162959</t>
+          <t>118481; 159862</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>60273; 82571</t>
+          <t>60622; 83655</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>61779; 92421</t>
+          <t>60172; 92431</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>64558; 99660</t>
+          <t>64076; 99420</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>70783; 108716</t>
+          <t>72456; 106094</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>82059; 121345</t>
+          <t>83966; 119816</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>116272; 156267</t>
+          <t>116985; 158159</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>141124; 187422</t>
+          <t>140131; 185219</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>126882; 171525</t>
+          <t>128172; 172621</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>81413; 209522</t>
+          <t>68158; 209067</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>185810; 239303</t>
+          <t>185431; 237247</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>214714; 272104</t>
+          <t>216648; 275707</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>208575; 268814</t>
+          <t>208947; 267175</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>159422; 304490</t>
+          <t>164664; 309086</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>80352; 116308</t>
+          <t>80039; 113094</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>91993; 133697</t>
+          <t>89944; 130238</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>74426; 110115</t>
+          <t>74294; 108109</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>116665; 662409</t>
+          <t>115396; 661787</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>142211; 189366</t>
+          <t>144524; 190325</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>151611; 199014</t>
+          <t>149607; 198951</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>139149; 188741</t>
+          <t>139291; 185893</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>157558; 197285</t>
+          <t>157241; 195440</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>233732; 293157</t>
+          <t>230488; 291258</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>256661; 319772</t>
+          <t>253752; 320843</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>224603; 284621</t>
+          <t>221945; 282856</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>304051; 941657</t>
+          <t>301573; 939413</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>333464; 400371</t>
+          <t>330433; 400334</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>459556; 544870</t>
+          <t>459374; 545048</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>433884; 512592</t>
+          <t>432584; 517136</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>494994; 1322586</t>
+          <t>492165; 1307074</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>675730; 775730</t>
+          <t>677917; 773902</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>849247; 954911</t>
+          <t>845311; 949794</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>748953; 855052</t>
+          <t>751578; 854512</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>619280; 823824</t>
+          <t>613111; 827942</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1030860; 1155726</t>
+          <t>1030826; 1145216</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1338548; 1480716</t>
+          <t>1337813; 1471272</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1211092; 1343531</t>
+          <t>1205297; 1339200</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1228718; 2206264</t>
+          <t>1229176; 2134927</t>
         </is>
       </c>
     </row>
